--- a/Windows_Ransomware_Intrusion/evidence/EventLogs/Microsoft-Windows-TerminalServices-LocalSessionManager.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/EventLogs/Microsoft-Windows-TerminalServices-LocalSessionManager.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\System\Event Logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/EventLogs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3EC3BDC-68A8-4FA3-B5A7-A21FB138AADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC772C3-8F61-DC42-B624-6577706380BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1176" windowWidth="15024" windowHeight="11064" xr2:uid="{DC4E9528-CB98-4161-A7BC-6BFDCA1E87D0}"/>
+    <workbookView xWindow="0" yWindow="1180" windowWidth="23800" windowHeight="16260" xr2:uid="{DC4E9528-CB98-4161-A7BC-6BFDCA1E87D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Microsoft-Windows-TerminalServi" sheetId="1" r:id="rId1"/>
@@ -620,7 +620,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -969,15 +969,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E2B9801-F2C7-4FFC-9216-7AD28548253C}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46136.777083333334</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46136.787499999999</v>
       </c>
